--- a/UTCUTS/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
+++ b/UTCUTS/A2_Extra_Inputs/A-Xtra_Scenarios.xlsx
@@ -821,5 +821,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E794D8A-7A48-4649-895B-E6353D00411E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC22CEC-6988-42C1-8517-4B812D7ADCAF}"/>
 </file>